--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="561">
   <si>
     <t>Property</t>
   </si>
@@ -1044,7 +1044,7 @@
     <t>Consent.patient.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>
@@ -1114,27 +1114,15 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://fhir.de/CodeSystem/identifier-type-de-basis"/&gt;
-    &lt;code value="KVZ10"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-kvid-2:Die type Codes 'GKV' und 'PKV' haben den Status 'retired', daher sollen diese nicht mehr verwendet werden {($this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='GKV') or $this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='PKV')).not()}</t>
-  </si>
-  <si>
     <t>CX.5</t>
   </si>
   <si>
@@ -1184,10 +1172,6 @@
   </si>
   <si>
     <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-kvid-1:Der unveränderliche Teil der KVID muss 10-stellig sein und mit einem Großbuchstaben anfangen {matches('^[A-Z][0-9]{9}$')}</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -1229,7 +1213,7 @@
     <t>Consent.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1266,7 +1250,7 @@
     <t>Consent.patient.identifier.assigner.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-iknr}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr}
 </t>
   </si>
   <si>
@@ -1352,10 +1336,6 @@
   </si>
   <si>
     <t xml:space="preserve">custodian
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -7096,7 +7076,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -7114,28 +7094,28 @@
         <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z44" t="s" s="2">
+      <c r="AA44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7147,13 +7127,13 @@
         <v>155</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>357</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>347</v>
@@ -7164,10 +7144,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7175,7 +7155,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -7193,65 +7173,65 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7269,10 +7249,10 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7280,10 +7260,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7291,7 +7271,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>87</v>
@@ -7309,13 +7289,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7329,64 +7309,64 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="U46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7394,10 +7374,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7420,16 +7400,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7479,7 +7459,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7491,16 +7471,16 @@
         <v>155</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7508,10 +7488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7534,16 +7514,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7593,7 +7573,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7611,10 +7591,10 @@
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7622,10 +7602,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7734,10 +7714,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7848,10 +7828,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7962,10 +7942,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8076,10 +8056,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8102,7 +8082,7 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>332</v>
@@ -8190,10 +8170,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8219,13 +8199,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8275,7 +8255,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8304,10 +8284,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8333,13 +8313,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8389,7 +8369,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8418,10 +8398,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8444,16 +8424,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8503,7 +8483,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8518,28 +8498,28 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>415</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8558,16 +8538,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8617,7 +8597,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8632,28 +8612,28 @@
         <v>311</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8672,16 +8652,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>428</v>
+        <v>385</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8731,7 +8711,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8746,24 +8726,24 @@
         <v>311</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8786,16 +8766,16 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8845,7 +8825,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8863,7 +8843,7 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>105</v>
@@ -8874,10 +8854,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8900,13 +8880,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8957,7 +8937,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8986,10 +8966,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9098,10 +9078,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9212,14 +9192,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9241,10 +9221,10 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>111</v>
@@ -9299,7 +9279,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9328,10 +9308,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9357,13 +9337,13 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9413,16 +9393,16 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI64" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>99</v>
@@ -9442,10 +9422,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9471,13 +9451,13 @@
         <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9527,7 +9507,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9536,7 +9516,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -9556,10 +9536,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9585,16 +9565,16 @@
         <v>228</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9623,7 +9603,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -9641,7 +9621,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9650,7 +9630,7 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -9670,10 +9650,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9696,13 +9676,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9753,7 +9733,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9782,10 +9762,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9894,10 +9874,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10008,14 +9988,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10037,10 +10017,10 @@
         <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>111</v>
@@ -10095,7 +10075,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10124,10 +10104,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10153,10 +10133,10 @@
         <v>282</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10207,7 +10187,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>87</v>
@@ -10236,10 +10216,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10262,16 +10242,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10321,7 +10301,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10342,7 +10322,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10350,10 +10330,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10376,13 +10356,13 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10433,7 +10413,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10462,10 +10442,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10488,13 +10468,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10545,7 +10525,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10574,10 +10554,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10686,10 +10666,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10800,14 +10780,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10829,10 +10809,10 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>111</v>
@@ -10887,7 +10867,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10916,10 +10896,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10945,10 +10925,10 @@
         <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10978,10 +10958,10 @@
         <v>220</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -10999,7 +10979,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11028,10 +11008,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11054,16 +11034,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11113,7 +11093,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11125,16 +11105,16 @@
         <v>155</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11142,10 +11122,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11168,13 +11148,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11182,7 +11162,7 @@
         <v>75</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>75</v>
@@ -11227,7 +11207,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11256,10 +11236,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11368,10 +11348,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11482,14 +11462,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11511,10 +11491,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>111</v>
@@ -11569,7 +11549,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11598,10 +11578,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11627,10 +11607,10 @@
         <v>228</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>231</v>
@@ -11662,10 +11642,10 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -11683,7 +11663,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -11712,10 +11692,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11738,16 +11718,16 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11797,7 +11777,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -11818,7 +11798,7 @@
         <v>75</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>75</v>
@@ -11826,10 +11806,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11855,20 +11835,20 @@
         <v>228</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>75</v>
@@ -11892,10 +11872,10 @@
         <v>162</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11913,7 +11893,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11942,10 +11922,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11971,13 +11951,13 @@
         <v>147</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12027,7 +12007,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12056,10 +12036,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12085,13 +12065,13 @@
         <v>147</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12120,10 +12100,10 @@
         <v>151</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -12141,7 +12121,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12170,10 +12150,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12199,13 +12179,13 @@
         <v>147</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12234,10 +12214,10 @@
         <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -12255,7 +12235,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12284,10 +12264,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12313,13 +12293,13 @@
         <v>228</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12348,10 +12328,10 @@
         <v>162</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -12369,7 +12349,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12398,10 +12378,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12424,16 +12404,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12483,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12495,16 +12475,16 @@
         <v>155</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>75</v>
@@ -12512,10 +12492,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12538,13 +12518,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12552,7 +12532,7 @@
         <v>75</v>
       </c>
       <c r="Q92" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="R92" t="s" s="2">
         <v>75</v>
@@ -12597,7 +12577,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12626,10 +12606,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12738,10 +12718,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12852,14 +12832,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12881,10 +12861,10 @@
         <v>108</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>111</v>
@@ -12939,7 +12919,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12968,10 +12948,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12997,10 +12977,10 @@
         <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13030,10 +13010,10 @@
         <v>220</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13051,7 +13031,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>87</v>
@@ -13080,10 +13060,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13106,16 +13086,16 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13165,7 +13145,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -13186,7 +13166,7 @@
         <v>75</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>75</v>
@@ -13194,10 +13174,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13223,10 +13203,10 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13277,7 +13257,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="565">
   <si>
     <t>Property</t>
   </si>
@@ -1044,7 +1044,7 @@
     <t>Consent.patient.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>
@@ -1114,15 +1114,27 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/CodeSystem/identifier-type-de-basis"/&gt;
+    &lt;code value="KVZ10"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://fhir.de/ValueSet/identifier-type-de-basis</t>
   </si>
   <si>
     <t>Identifier.type</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+kvid-2:Die type Codes 'GKV' und 'PKV' haben den Status 'retired', daher sollen diese nicht mehr verwendet werden {($this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='GKV') or $this.coding.exists(system='http://fhir.de/CodeSystem/identifier-type-de-basis' and code='PKV')).not()}</t>
+  </si>
+  <si>
     <t>CX.5</t>
   </si>
   <si>
@@ -1172,6 +1184,10 @@
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+kvid-1:Der unveränderliche Teil der KVID muss 10-stellig sein und mit einem Großbuchstaben anfangen {matches('^[A-Z][0-9]{9}$')}</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -1213,7 +1229,7 @@
     <t>Consent.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1250,7 +1266,7 @@
     <t>Consent.patient.identifier.assigner.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-iknr}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-iknr}
 </t>
   </si>
   <si>
@@ -1336,6 +1352,10 @@
   </si>
   <si>
     <t xml:space="preserve">custodian
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -7076,7 +7096,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -7094,10 +7114,10 @@
         <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -7115,7 +7135,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7127,13 +7147,13 @@
         <v>155</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>347</v>
@@ -7144,10 +7164,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7155,7 +7175,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -7173,29 +7193,29 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7231,7 +7251,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7249,10 +7269,10 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7260,10 +7280,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7271,7 +7291,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>87</v>
@@ -7289,13 +7309,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7309,7 +7329,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7345,7 +7365,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7357,16 +7377,16 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>375</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7374,10 +7394,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7400,16 +7420,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7459,7 +7479,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7471,16 +7491,16 @@
         <v>155</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7488,10 +7508,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7514,16 +7534,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7573,7 +7593,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7591,10 +7611,10 @@
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7602,10 +7622,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7714,10 +7734,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7828,10 +7848,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7942,10 +7962,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8056,10 +8076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8082,7 +8102,7 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>332</v>
@@ -8170,10 +8190,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8199,13 +8219,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8255,7 +8275,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8284,10 +8304,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8313,13 +8333,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8369,7 +8389,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8398,10 +8418,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8424,16 +8444,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8483,7 +8503,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8498,28 +8518,28 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8538,16 +8558,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8597,7 +8617,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8612,28 +8632,28 @@
         <v>311</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8652,16 +8672,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8711,7 +8731,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8726,24 +8746,24 @@
         <v>311</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8766,16 +8786,16 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8825,7 +8845,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8843,7 +8863,7 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>105</v>
@@ -8854,10 +8874,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8880,13 +8900,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8937,7 +8957,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8966,10 +8986,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9078,10 +9098,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9192,14 +9212,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9221,10 +9241,10 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>111</v>
@@ -9279,7 +9299,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9308,10 +9328,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9337,13 +9357,13 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9393,7 +9413,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9402,7 +9422,7 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>99</v>
@@ -9422,10 +9442,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9451,13 +9471,13 @@
         <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9507,7 +9527,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9516,7 +9536,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -9536,10 +9556,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9565,16 +9585,16 @@
         <v>228</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9603,7 +9623,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -9621,7 +9641,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9630,7 +9650,7 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -9650,10 +9670,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9676,13 +9696,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9733,7 +9753,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9762,10 +9782,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9874,10 +9894,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9988,14 +10008,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10017,10 +10037,10 @@
         <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>111</v>
@@ -10075,7 +10095,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10104,10 +10124,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10133,10 +10153,10 @@
         <v>282</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10187,7 +10207,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>87</v>
@@ -10216,10 +10236,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10242,16 +10262,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10301,7 +10321,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10322,7 +10342,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10330,10 +10350,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10356,13 +10376,13 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10413,7 +10433,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10442,10 +10462,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10468,13 +10488,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10525,7 +10545,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10554,10 +10574,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10666,10 +10686,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10780,14 +10800,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10809,10 +10829,10 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>111</v>
@@ -10867,7 +10887,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10896,10 +10916,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10925,10 +10945,10 @@
         <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10958,28 +10978,28 @@
         <v>220</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="Z78" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11008,10 +11028,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11034,16 +11054,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11093,7 +11113,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11105,16 +11125,16 @@
         <v>155</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11122,10 +11142,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11148,13 +11168,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11162,7 +11182,7 @@
         <v>75</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>75</v>
@@ -11207,7 +11227,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11236,10 +11256,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11348,10 +11368,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11462,14 +11482,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11491,10 +11511,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>111</v>
@@ -11549,7 +11569,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11578,10 +11598,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11607,10 +11627,10 @@
         <v>228</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>231</v>
@@ -11642,28 +11662,28 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="Z84" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -11692,10 +11712,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11718,16 +11738,16 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11777,7 +11797,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -11798,7 +11818,7 @@
         <v>75</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>75</v>
@@ -11806,10 +11826,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11835,20 +11855,20 @@
         <v>228</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>75</v>
@@ -11872,10 +11892,10 @@
         <v>162</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11893,7 +11913,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11922,10 +11942,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11951,13 +11971,13 @@
         <v>147</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12007,7 +12027,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12036,10 +12056,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12065,13 +12085,13 @@
         <v>147</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12100,28 +12120,28 @@
         <v>151</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12150,10 +12170,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12179,13 +12199,13 @@
         <v>147</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12214,28 +12234,28 @@
         <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12264,10 +12284,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12293,13 +12313,13 @@
         <v>228</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12328,28 +12348,28 @@
         <v>162</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12378,10 +12398,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12404,16 +12424,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12463,7 +12483,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12475,16 +12495,16 @@
         <v>155</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>75</v>
@@ -12492,10 +12512,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12518,13 +12538,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12532,7 +12552,7 @@
         <v>75</v>
       </c>
       <c r="Q92" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="R92" t="s" s="2">
         <v>75</v>
@@ -12577,7 +12597,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12606,10 +12626,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12718,10 +12738,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12832,14 +12852,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12861,10 +12881,10 @@
         <v>108</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>111</v>
@@ -12919,7 +12939,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12948,10 +12968,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12977,10 +12997,10 @@
         <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13010,28 +13030,28 @@
         <v>220</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="Z96" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>87</v>
@@ -13060,10 +13080,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13086,16 +13106,16 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13145,7 +13165,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -13166,7 +13186,7 @@
         <v>75</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>75</v>
@@ -13174,10 +13194,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13203,10 +13223,10 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13257,7 +13277,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
